--- a/example/tax_report_2019_daily_rates.xlsx
+++ b/example/tax_report_2019_daily_rates.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>Symbol</t>
   </si>
@@ -83,10 +83,10 @@
     <t>156.00 USD</t>
   </si>
   <si>
-    <t>ELSTER - Anlage</t>
-  </si>
-  <si>
-    <t>ELSTER - Zeile (Suggestion!)</t>
+    <t>ELSTER – Anlage</t>
+  </si>
+  <si>
+    <t>ELSTER – Zeile</t>
   </si>
   <si>
     <t>Value</t>
@@ -98,9 +98,6 @@
     <t>Anlage N</t>
   </si>
   <si>
-    <t>Anlage SO</t>
-  </si>
-  <si>
     <t>Zeile 19: Ausländische Kapitalerträge (ohne Betrag lt. Zeile 47)</t>
   </si>
   <si>
@@ -114,15 +111,6 @@
   </si>
   <si>
     <t>Zeile 65: (Werbungskosten Sonstiges): Überweisungsgebühren auf deutsches Konto für Gehaltsbestandteil RSU/ESPP</t>
-  </si>
-  <si>
-    <t>Zeilen 48 - 54: Gewinn / Verlust aus Verkauf von Fremdwährungen</t>
-  </si>
-  <si>
-    <t>Zeilen 48 - 54: Veräußerungswert Fremdwährungen</t>
-  </si>
-  <si>
-    <t>Zeilen 48 - 54: Anschaffungskosten Fremdwährungen</t>
   </si>
 </sst>
 </file>
@@ -617,10 +605,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="105.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
   </cols>
@@ -641,7 +629,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2">
         <v>329.69</v>
@@ -652,7 +640,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>329.69</v>
@@ -663,7 +651,7 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -674,7 +662,7 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -685,42 +673,9 @@
         <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9">
         <v>0</v>
       </c>
     </row>
